--- a/Models/Лошади/results/Лошади - Лучшие модели.xlsx
+++ b/Models/Лошади/results/Лошади - Лучшие модели.xlsx
@@ -462,17 +462,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="C2" t="n">
-        <v>5.15</v>
+        <v>5.08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.46</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="C3" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10.82</v>
+        <v>9.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>9.07</v>
+        <v>10.08</v>
       </c>
       <c r="D4" t="n">
-        <v>29.28</v>
+        <v>31.63</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.41</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>6.6</v>
+        <v>7.69</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44</v>
+        <v>15.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.31</v>
+        <v>18.27</v>
       </c>
       <c r="C6" t="n">
-        <v>18.16</v>
+        <v>12.36</v>
       </c>
       <c r="D6" t="n">
-        <v>34.6</v>
+        <v>25.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3.86610369321697e+18</v>
+        <v>5.961066683118794e+20</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.23</v>
+        <v>25.41</v>
       </c>
       <c r="C8" t="n">
-        <v>31.94</v>
+        <v>22.23</v>
       </c>
       <c r="D8" t="n">
-        <v>42.89</v>
+        <v>29.52</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -605,17 +605,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.85</v>
+        <v>49.18</v>
       </c>
       <c r="C9" t="n">
-        <v>76.20999999999999</v>
+        <v>91.95</v>
       </c>
       <c r="D9" t="n">
-        <v>43.07</v>
+        <v>75.19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.5</v>
+        <v>3.12</v>
       </c>
       <c r="C10" t="n">
-        <v>5.01</v>
+        <v>3.74</v>
       </c>
       <c r="D10" t="n">
-        <v>8.130000000000001</v>
+        <v>6.41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.54</v>
+        <v>5.29</v>
       </c>
       <c r="C11" t="n">
-        <v>5.51</v>
+        <v>4.89</v>
       </c>
       <c r="D11" t="n">
-        <v>12.78</v>
+        <v>10.76</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.27</v>
+        <v>10.47</v>
       </c>
       <c r="C12" t="n">
-        <v>11.06</v>
+        <v>5.95</v>
       </c>
       <c r="D12" t="n">
-        <v>21.38</v>
+        <v>23.86</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -689,17 +689,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.34</v>
+        <v>8.34</v>
       </c>
       <c r="C13" t="n">
-        <v>15.55</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>12.24</v>
+        <v>8.68</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.18</v>
+        <v>12.51</v>
       </c>
       <c r="C14" t="n">
-        <v>18.22</v>
+        <v>12.07</v>
       </c>
       <c r="D14" t="n">
-        <v>22.1</v>
+        <v>17.59</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -731,17 +731,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.52</v>
+        <v>20.61</v>
       </c>
       <c r="C15" t="n">
-        <v>5.68</v>
+        <v>27.49</v>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>25.06</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.71</v>
+        <v>10.64</v>
       </c>
       <c r="C16" t="n">
-        <v>30.04</v>
+        <v>13.06</v>
       </c>
       <c r="D16" t="n">
-        <v>49.21</v>
+        <v>22.44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -773,17 +773,17 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="C17" t="n">
-        <v>73.38</v>
+        <v>4.11</v>
       </c>
       <c r="D17" t="n">
-        <v>92.33</v>
+        <v>11.78</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="C18" t="n">
-        <v>94.63</v>
+        <v>8.5</v>
       </c>
       <c r="D18" t="n">
-        <v>73.56999999999999</v>
+        <v>12.48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -815,17 +815,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25.8</v>
+        <v>20.12</v>
       </c>
       <c r="C19" t="n">
-        <v>29.42</v>
+        <v>21.84</v>
       </c>
       <c r="D19" t="n">
-        <v>21.06</v>
+        <v>23.44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.1</v>
+        <v>4.61</v>
       </c>
       <c r="C20" t="n">
-        <v>5.04</v>
+        <v>4.36</v>
       </c>
       <c r="D20" t="n">
-        <v>9.630000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,17 +857,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.13</v>
+        <v>19.89</v>
       </c>
       <c r="C21" t="n">
-        <v>20.01</v>
+        <v>9.68</v>
       </c>
       <c r="D21" t="n">
-        <v>27.23</v>
+        <v>17.39</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
